--- a/southern_europe/italy_data/network_capex_metrics/pipeline_size_class_connections.xlsx
+++ b/southern_europe/italy_data/network_capex_metrics/pipeline_size_class_connections.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS45"/>
+  <dimension ref="A1:AV48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,6 +563,15 @@
       <c r="AS1" s="1" t="n">
         <v>44</v>
       </c>
+      <c r="AT1" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="AU1" s="1" t="n">
+        <v>46</v>
+      </c>
+      <c r="AV1" s="1" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -698,6 +707,15 @@
         <v>1</v>
       </c>
       <c r="AS2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -837,6 +855,15 @@
       <c r="AS3" t="n">
         <v>1</v>
       </c>
+      <c r="AT3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -974,6 +1001,15 @@
       <c r="AS4" t="n">
         <v>1</v>
       </c>
+      <c r="AT4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -1111,6 +1147,15 @@
       <c r="AS5" t="n">
         <v>1</v>
       </c>
+      <c r="AT5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -1248,6 +1293,15 @@
       <c r="AS6" t="n">
         <v>1</v>
       </c>
+      <c r="AT6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -1385,6 +1439,15 @@
       <c r="AS7" t="n">
         <v>1</v>
       </c>
+      <c r="AT7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -1522,6 +1585,15 @@
       <c r="AS8" t="n">
         <v>1</v>
       </c>
+      <c r="AT8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -1659,6 +1731,15 @@
       <c r="AS9" t="n">
         <v>1</v>
       </c>
+      <c r="AT9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -1796,6 +1877,15 @@
       <c r="AS10" t="n">
         <v>1</v>
       </c>
+      <c r="AT10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -1933,6 +2023,15 @@
       <c r="AS11" t="n">
         <v>1</v>
       </c>
+      <c r="AT11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -2070,6 +2169,15 @@
       <c r="AS12" t="n">
         <v>1</v>
       </c>
+      <c r="AT12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -2207,6 +2315,15 @@
       <c r="AS13" t="n">
         <v>1</v>
       </c>
+      <c r="AT13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -2344,6 +2461,15 @@
       <c r="AS14" t="n">
         <v>1</v>
       </c>
+      <c r="AT14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -2481,6 +2607,15 @@
       <c r="AS15" t="n">
         <v>1</v>
       </c>
+      <c r="AT15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -2618,6 +2753,15 @@
       <c r="AS16" t="n">
         <v>1</v>
       </c>
+      <c r="AT16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -2755,6 +2899,15 @@
       <c r="AS17" t="n">
         <v>1</v>
       </c>
+      <c r="AT17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -2892,6 +3045,15 @@
       <c r="AS18" t="n">
         <v>1</v>
       </c>
+      <c r="AT18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -3029,6 +3191,15 @@
       <c r="AS19" t="n">
         <v>1</v>
       </c>
+      <c r="AT19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -3166,6 +3337,15 @@
       <c r="AS20" t="n">
         <v>1</v>
       </c>
+      <c r="AT20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -3303,6 +3483,15 @@
       <c r="AS21" t="n">
         <v>1</v>
       </c>
+      <c r="AT21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -3440,6 +3629,15 @@
       <c r="AS22" t="n">
         <v>1</v>
       </c>
+      <c r="AT22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -3577,6 +3775,15 @@
       <c r="AS23" t="n">
         <v>1</v>
       </c>
+      <c r="AT23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -3714,6 +3921,15 @@
       <c r="AS24" t="n">
         <v>1</v>
       </c>
+      <c r="AT24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -3851,6 +4067,15 @@
       <c r="AS25" t="n">
         <v>1</v>
       </c>
+      <c r="AT25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -3941,7 +4166,7 @@
         <v>1</v>
       </c>
       <c r="AD26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -3986,6 +4211,15 @@
         <v>1</v>
       </c>
       <c r="AS26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4125,6 +4359,15 @@
       <c r="AS27" t="n">
         <v>1</v>
       </c>
+      <c r="AT27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -4262,6 +4505,15 @@
       <c r="AS28" t="n">
         <v>1</v>
       </c>
+      <c r="AT28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -4361,7 +4613,7 @@
         <v>1</v>
       </c>
       <c r="AG29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
         <v>0</v>
@@ -4397,6 +4649,15 @@
         <v>1</v>
       </c>
       <c r="AS29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV29" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4507,7 +4768,7 @@
         <v>1</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
         <v>1</v>
@@ -4534,6 +4795,15 @@
         <v>1</v>
       </c>
       <c r="AS30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV30" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4673,6 +4943,15 @@
       <c r="AS31" t="n">
         <v>1</v>
       </c>
+      <c r="AT31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -4810,6 +5089,15 @@
       <c r="AS32" t="n">
         <v>1</v>
       </c>
+      <c r="AT32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -4891,7 +5179,7 @@
         <v>1</v>
       </c>
       <c r="AA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
         <v>1</v>
@@ -4945,6 +5233,15 @@
         <v>1</v>
       </c>
       <c r="AS33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV33" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5084,6 +5381,15 @@
       <c r="AS34" t="n">
         <v>1</v>
       </c>
+      <c r="AT34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -5221,6 +5527,15 @@
       <c r="AS35" t="n">
         <v>1</v>
       </c>
+      <c r="AT35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -5358,6 +5673,15 @@
       <c r="AS36" t="n">
         <v>1</v>
       </c>
+      <c r="AT36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -5495,6 +5819,15 @@
       <c r="AS37" t="n">
         <v>1</v>
       </c>
+      <c r="AT37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -5632,6 +5965,15 @@
       <c r="AS38" t="n">
         <v>1</v>
       </c>
+      <c r="AT38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -5769,6 +6111,15 @@
       <c r="AS39" t="n">
         <v>1</v>
       </c>
+      <c r="AT39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -5906,6 +6257,15 @@
       <c r="AS40" t="n">
         <v>1</v>
       </c>
+      <c r="AT40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
@@ -6043,6 +6403,15 @@
       <c r="AS41" t="n">
         <v>1</v>
       </c>
+      <c r="AT41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
@@ -6180,6 +6549,15 @@
       <c r="AS42" t="n">
         <v>1</v>
       </c>
+      <c r="AT42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
@@ -6317,6 +6695,15 @@
       <c r="AS43" t="n">
         <v>1</v>
       </c>
+      <c r="AT43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
@@ -6454,6 +6841,15 @@
       <c r="AS44" t="n">
         <v>1</v>
       </c>
+      <c r="AT44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
@@ -6589,6 +6985,453 @@
         <v>1</v>
       </c>
       <c r="AS45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" t="n">
+        <v>1</v>
+      </c>
+      <c r="K46" t="n">
+        <v>1</v>
+      </c>
+      <c r="L46" t="n">
+        <v>1</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1</v>
+      </c>
+      <c r="N46" t="n">
+        <v>1</v>
+      </c>
+      <c r="O46" t="n">
+        <v>1</v>
+      </c>
+      <c r="P46" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>1</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1</v>
+      </c>
+      <c r="S46" t="n">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1</v>
+      </c>
+      <c r="X46" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" t="n">
+        <v>1</v>
+      </c>
+      <c r="K47" t="n">
+        <v>1</v>
+      </c>
+      <c r="L47" t="n">
+        <v>1</v>
+      </c>
+      <c r="M47" t="n">
+        <v>1</v>
+      </c>
+      <c r="N47" t="n">
+        <v>1</v>
+      </c>
+      <c r="O47" t="n">
+        <v>1</v>
+      </c>
+      <c r="P47" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>1</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1</v>
+      </c>
+      <c r="S47" t="n">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1</v>
+      </c>
+      <c r="X47" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>1</v>
+      </c>
+      <c r="M48" t="n">
+        <v>1</v>
+      </c>
+      <c r="N48" t="n">
+        <v>1</v>
+      </c>
+      <c r="O48" t="n">
+        <v>1</v>
+      </c>
+      <c r="P48" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>1</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1</v>
+      </c>
+      <c r="S48" t="n">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1</v>
+      </c>
+      <c r="X48" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV48" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6603,7 +7446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS45"/>
+  <dimension ref="A1:AV48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6739,6 +7582,15 @@
       <c r="AS1" s="1" t="n">
         <v>44</v>
       </c>
+      <c r="AT1" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="AU1" s="1" t="n">
+        <v>46</v>
+      </c>
+      <c r="AV1" s="1" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -6874,6 +7726,15 @@
         <v>1</v>
       </c>
       <c r="AS2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7013,6 +7874,15 @@
       <c r="AS3" t="n">
         <v>1</v>
       </c>
+      <c r="AT3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -7150,6 +8020,15 @@
       <c r="AS4" t="n">
         <v>1</v>
       </c>
+      <c r="AT4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -7287,6 +8166,15 @@
       <c r="AS5" t="n">
         <v>1</v>
       </c>
+      <c r="AT5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -7424,6 +8312,15 @@
       <c r="AS6" t="n">
         <v>1</v>
       </c>
+      <c r="AT6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -7561,6 +8458,15 @@
       <c r="AS7" t="n">
         <v>1</v>
       </c>
+      <c r="AT7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -7698,6 +8604,15 @@
       <c r="AS8" t="n">
         <v>1</v>
       </c>
+      <c r="AT8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -7835,6 +8750,15 @@
       <c r="AS9" t="n">
         <v>1</v>
       </c>
+      <c r="AT9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -7972,6 +8896,15 @@
       <c r="AS10" t="n">
         <v>1</v>
       </c>
+      <c r="AT10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -8109,6 +9042,15 @@
       <c r="AS11" t="n">
         <v>1</v>
       </c>
+      <c r="AT11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -8246,6 +9188,15 @@
       <c r="AS12" t="n">
         <v>1</v>
       </c>
+      <c r="AT12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -8383,6 +9334,15 @@
       <c r="AS13" t="n">
         <v>1</v>
       </c>
+      <c r="AT13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -8520,6 +9480,15 @@
       <c r="AS14" t="n">
         <v>1</v>
       </c>
+      <c r="AT14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -8657,6 +9626,15 @@
       <c r="AS15" t="n">
         <v>1</v>
       </c>
+      <c r="AT15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -8794,6 +9772,15 @@
       <c r="AS16" t="n">
         <v>1</v>
       </c>
+      <c r="AT16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -8931,6 +9918,15 @@
       <c r="AS17" t="n">
         <v>1</v>
       </c>
+      <c r="AT17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -9068,6 +10064,15 @@
       <c r="AS18" t="n">
         <v>1</v>
       </c>
+      <c r="AT18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -9205,6 +10210,15 @@
       <c r="AS19" t="n">
         <v>1</v>
       </c>
+      <c r="AT19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -9342,6 +10356,15 @@
       <c r="AS20" t="n">
         <v>1</v>
       </c>
+      <c r="AT20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -9479,6 +10502,15 @@
       <c r="AS21" t="n">
         <v>1</v>
       </c>
+      <c r="AT21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -9616,6 +10648,15 @@
       <c r="AS22" t="n">
         <v>1</v>
       </c>
+      <c r="AT22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -9753,6 +10794,15 @@
       <c r="AS23" t="n">
         <v>1</v>
       </c>
+      <c r="AT23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -9890,6 +10940,15 @@
       <c r="AS24" t="n">
         <v>1</v>
       </c>
+      <c r="AT24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -10027,6 +11086,15 @@
       <c r="AS25" t="n">
         <v>1</v>
       </c>
+      <c r="AT25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -10164,6 +11232,15 @@
       <c r="AS26" t="n">
         <v>1</v>
       </c>
+      <c r="AT26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -10301,6 +11378,15 @@
       <c r="AS27" t="n">
         <v>1</v>
       </c>
+      <c r="AT27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -10438,6 +11524,15 @@
       <c r="AS28" t="n">
         <v>1</v>
       </c>
+      <c r="AT28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -10575,6 +11670,15 @@
       <c r="AS29" t="n">
         <v>1</v>
       </c>
+      <c r="AT29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -10683,7 +11787,7 @@
         <v>1</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
         <v>1</v>
@@ -10710,6 +11814,15 @@
         <v>1</v>
       </c>
       <c r="AS30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV30" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10849,6 +11962,15 @@
       <c r="AS31" t="n">
         <v>1</v>
       </c>
+      <c r="AT31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -10986,6 +12108,15 @@
       <c r="AS32" t="n">
         <v>1</v>
       </c>
+      <c r="AT32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -11123,6 +12254,15 @@
       <c r="AS33" t="n">
         <v>1</v>
       </c>
+      <c r="AT33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
@@ -11260,6 +12400,15 @@
       <c r="AS34" t="n">
         <v>1</v>
       </c>
+      <c r="AT34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -11397,6 +12546,15 @@
       <c r="AS35" t="n">
         <v>1</v>
       </c>
+      <c r="AT35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -11534,6 +12692,15 @@
       <c r="AS36" t="n">
         <v>1</v>
       </c>
+      <c r="AT36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -11671,6 +12838,15 @@
       <c r="AS37" t="n">
         <v>1</v>
       </c>
+      <c r="AT37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -11808,6 +12984,15 @@
       <c r="AS38" t="n">
         <v>1</v>
       </c>
+      <c r="AT38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -11945,6 +13130,15 @@
       <c r="AS39" t="n">
         <v>1</v>
       </c>
+      <c r="AT39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -12082,6 +13276,15 @@
       <c r="AS40" t="n">
         <v>1</v>
       </c>
+      <c r="AT40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
@@ -12219,6 +13422,15 @@
       <c r="AS41" t="n">
         <v>1</v>
       </c>
+      <c r="AT41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
@@ -12356,6 +13568,15 @@
       <c r="AS42" t="n">
         <v>1</v>
       </c>
+      <c r="AT42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
@@ -12493,6 +13714,15 @@
       <c r="AS43" t="n">
         <v>1</v>
       </c>
+      <c r="AT43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
@@ -12630,6 +13860,15 @@
       <c r="AS44" t="n">
         <v>1</v>
       </c>
+      <c r="AT44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
@@ -12765,6 +14004,453 @@
         <v>1</v>
       </c>
       <c r="AS45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" t="n">
+        <v>1</v>
+      </c>
+      <c r="K46" t="n">
+        <v>1</v>
+      </c>
+      <c r="L46" t="n">
+        <v>1</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1</v>
+      </c>
+      <c r="N46" t="n">
+        <v>1</v>
+      </c>
+      <c r="O46" t="n">
+        <v>1</v>
+      </c>
+      <c r="P46" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>1</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1</v>
+      </c>
+      <c r="S46" t="n">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1</v>
+      </c>
+      <c r="X46" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" t="n">
+        <v>1</v>
+      </c>
+      <c r="K47" t="n">
+        <v>1</v>
+      </c>
+      <c r="L47" t="n">
+        <v>1</v>
+      </c>
+      <c r="M47" t="n">
+        <v>1</v>
+      </c>
+      <c r="N47" t="n">
+        <v>1</v>
+      </c>
+      <c r="O47" t="n">
+        <v>1</v>
+      </c>
+      <c r="P47" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>1</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1</v>
+      </c>
+      <c r="S47" t="n">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1</v>
+      </c>
+      <c r="X47" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1</v>
+      </c>
+      <c r="L48" t="n">
+        <v>1</v>
+      </c>
+      <c r="M48" t="n">
+        <v>1</v>
+      </c>
+      <c r="N48" t="n">
+        <v>1</v>
+      </c>
+      <c r="O48" t="n">
+        <v>1</v>
+      </c>
+      <c r="P48" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>1</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1</v>
+      </c>
+      <c r="S48" t="n">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1</v>
+      </c>
+      <c r="X48" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV48" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12779,7 +14465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS45"/>
+  <dimension ref="A1:AV48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12915,6 +14601,15 @@
       <c r="AS1" s="1" t="n">
         <v>44</v>
       </c>
+      <c r="AT1" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="AU1" s="1" t="n">
+        <v>46</v>
+      </c>
+      <c r="AV1" s="1" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -13050,6 +14745,15 @@
         <v>1</v>
       </c>
       <c r="AS2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13189,6 +14893,15 @@
       <c r="AS3" t="n">
         <v>1</v>
       </c>
+      <c r="AT3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -13326,6 +15039,15 @@
       <c r="AS4" t="n">
         <v>1</v>
       </c>
+      <c r="AT4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -13463,6 +15185,15 @@
       <c r="AS5" t="n">
         <v>1</v>
       </c>
+      <c r="AT5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -13600,6 +15331,15 @@
       <c r="AS6" t="n">
         <v>1</v>
       </c>
+      <c r="AT6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -13737,6 +15477,15 @@
       <c r="AS7" t="n">
         <v>1</v>
       </c>
+      <c r="AT7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -13874,6 +15623,15 @@
       <c r="AS8" t="n">
         <v>1</v>
       </c>
+      <c r="AT8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -14011,6 +15769,15 @@
       <c r="AS9" t="n">
         <v>1</v>
       </c>
+      <c r="AT9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -14148,6 +15915,15 @@
       <c r="AS10" t="n">
         <v>1</v>
       </c>
+      <c r="AT10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -14285,6 +16061,15 @@
       <c r="AS11" t="n">
         <v>1</v>
       </c>
+      <c r="AT11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -14422,6 +16207,15 @@
       <c r="AS12" t="n">
         <v>1</v>
       </c>
+      <c r="AT12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -14559,6 +16353,15 @@
       <c r="AS13" t="n">
         <v>1</v>
       </c>
+      <c r="AT13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -14696,6 +16499,15 @@
       <c r="AS14" t="n">
         <v>1</v>
       </c>
+      <c r="AT14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -14833,6 +16645,15 @@
       <c r="AS15" t="n">
         <v>1</v>
       </c>
+      <c r="AT15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -14970,6 +16791,15 @@
       <c r="AS16" t="n">
         <v>1</v>
       </c>
+      <c r="AT16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -15107,6 +16937,15 @@
       <c r="AS17" t="n">
         <v>1</v>
       </c>
+      <c r="AT17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -15244,6 +17083,15 @@
       <c r="AS18" t="n">
         <v>1</v>
       </c>
+      <c r="AT18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -15381,6 +17229,15 @@
       <c r="AS19" t="n">
         <v>1</v>
       </c>
+      <c r="AT19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -15518,6 +17375,15 @@
       <c r="AS20" t="n">
         <v>1</v>
       </c>
+      <c r="AT20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -15655,6 +17521,15 @@
       <c r="AS21" t="n">
         <v>1</v>
       </c>
+      <c r="AT21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -15792,6 +17667,15 @@
       <c r="AS22" t="n">
         <v>1</v>
       </c>
+      <c r="AT22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -15929,6 +17813,15 @@
       <c r="AS23" t="n">
         <v>1</v>
       </c>
+      <c r="AT23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -16066,6 +17959,15 @@
       <c r="AS24" t="n">
         <v>1</v>
       </c>
+      <c r="AT24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -16203,6 +18105,15 @@
       <c r="AS25" t="n">
         <v>1</v>
       </c>
+      <c r="AT25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -16340,6 +18251,15 @@
       <c r="AS26" t="n">
         <v>1</v>
       </c>
+      <c r="AT26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -16477,6 +18397,15 @@
       <c r="AS27" t="n">
         <v>1</v>
       </c>
+      <c r="AT27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -16614,6 +18543,15 @@
       <c r="AS28" t="n">
         <v>1</v>
       </c>
+      <c r="AT28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -16713,7 +18651,7 @@
         <v>1</v>
       </c>
       <c r="AG29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
         <v>0</v>
@@ -16749,6 +18687,15 @@
         <v>1</v>
       </c>
       <c r="AS29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV29" t="n">
         <v>1</v>
       </c>
     </row>
@@ -16859,7 +18806,7 @@
         <v>1</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
         <v>1</v>
@@ -16886,6 +18833,15 @@
         <v>1</v>
       </c>
       <c r="AS30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV30" t="n">
         <v>1</v>
       </c>
     </row>
@@ -17025,6 +18981,15 @@
       <c r="AS31" t="n">
         <v>1</v>
       </c>
+      <c r="AT31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -17162,6 +19127,15 @@
       <c r="AS32" t="n">
         <v>1</v>
       </c>
+      <c r="AT32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -17243,7 +19217,7 @@
         <v>1</v>
       </c>
       <c r="AA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
         <v>1</v>
@@ -17297,6 +19271,15 @@
         <v>1</v>
       </c>
       <c r="AS33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV33" t="n">
         <v>1</v>
       </c>
     </row>
@@ -17436,6 +19419,15 @@
       <c r="AS34" t="n">
         <v>1</v>
       </c>
+      <c r="AT34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -17573,6 +19565,15 @@
       <c r="AS35" t="n">
         <v>1</v>
       </c>
+      <c r="AT35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -17710,6 +19711,15 @@
       <c r="AS36" t="n">
         <v>1</v>
       </c>
+      <c r="AT36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -17847,6 +19857,15 @@
       <c r="AS37" t="n">
         <v>1</v>
       </c>
+      <c r="AT37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -17984,6 +20003,15 @@
       <c r="AS38" t="n">
         <v>1</v>
       </c>
+      <c r="AT38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -18121,6 +20149,15 @@
       <c r="AS39" t="n">
         <v>1</v>
       </c>
+      <c r="AT39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -18258,6 +20295,15 @@
       <c r="AS40" t="n">
         <v>1</v>
       </c>
+      <c r="AT40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
@@ -18395,6 +20441,15 @@
       <c r="AS41" t="n">
         <v>1</v>
       </c>
+      <c r="AT41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
@@ -18532,6 +20587,15 @@
       <c r="AS42" t="n">
         <v>1</v>
       </c>
+      <c r="AT42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
@@ -18669,6 +20733,15 @@
       <c r="AS43" t="n">
         <v>1</v>
       </c>
+      <c r="AT43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
@@ -18806,6 +20879,15 @@
       <c r="AS44" t="n">
         <v>1</v>
       </c>
+      <c r="AT44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
@@ -18941,6 +21023,453 @@
         <v>1</v>
       </c>
       <c r="AS45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" t="n">
+        <v>1</v>
+      </c>
+      <c r="K46" t="n">
+        <v>1</v>
+      </c>
+      <c r="L46" t="n">
+        <v>1</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1</v>
+      </c>
+      <c r="N46" t="n">
+        <v>1</v>
+      </c>
+      <c r="O46" t="n">
+        <v>1</v>
+      </c>
+      <c r="P46" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>1</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1</v>
+      </c>
+      <c r="S46" t="n">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1</v>
+      </c>
+      <c r="X46" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" t="n">
+        <v>1</v>
+      </c>
+      <c r="K47" t="n">
+        <v>1</v>
+      </c>
+      <c r="L47" t="n">
+        <v>1</v>
+      </c>
+      <c r="M47" t="n">
+        <v>1</v>
+      </c>
+      <c r="N47" t="n">
+        <v>1</v>
+      </c>
+      <c r="O47" t="n">
+        <v>1</v>
+      </c>
+      <c r="P47" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>1</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1</v>
+      </c>
+      <c r="S47" t="n">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1</v>
+      </c>
+      <c r="X47" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1</v>
+      </c>
+      <c r="L48" t="n">
+        <v>1</v>
+      </c>
+      <c r="M48" t="n">
+        <v>1</v>
+      </c>
+      <c r="N48" t="n">
+        <v>1</v>
+      </c>
+      <c r="O48" t="n">
+        <v>1</v>
+      </c>
+      <c r="P48" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>1</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1</v>
+      </c>
+      <c r="S48" t="n">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1</v>
+      </c>
+      <c r="X48" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV48" t="n">
         <v>1</v>
       </c>
     </row>

--- a/southern_europe/italy_data/network_capex_metrics/pipeline_size_class_connections.xlsx
+++ b/southern_europe/italy_data/network_capex_metrics/pipeline_size_class_connections.xlsx
@@ -3427,7 +3427,7 @@
         <v>1</v>
       </c>
       <c r="AA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
         <v>1</v>
@@ -3570,7 +3570,7 @@
         <v>1</v>
       </c>
       <c r="Z22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
         <v>1</v>
@@ -5507,7 +5507,7 @@
         <v>1</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN35" t="n">
         <v>1</v>
